--- a/docs/quick_start_files/code examples/wdi_4_indicators.xlsx
+++ b/docs/quick_start_files/code examples/wdi_4_indicators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/odupriez_worldbank_org/Documents/_OD/ANOMALY/WDI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{EE2325A4-CA0F-4420-8211-B473FC7F12AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE5C423D-3E43-449A-B0B3-BB6D07278285}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{EE2325A4-CA0F-4420-8211-B473FC7F12AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C361897D-F6F5-4674-9EC1-3C43BB46706D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{72EACD0A-85B6-4577-8C48-58C6D5752762}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="124">
   <si>
     <t>Country.Name</t>
   </si>
@@ -225,9 +225,6 @@
   </si>
   <si>
     <t>X2023</t>
-  </si>
-  <si>
-    <t>X2024</t>
   </si>
   <si>
     <t>Belgium</t>
@@ -995,6 +992,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1314,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FBC034-A655-4DD7-A2A6-9BFE83029FCF}">
-  <dimension ref="A1:BQ13"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.1328125" bestFit="1" customWidth="1"/>
@@ -1323,7 +1324,7 @@
     <col min="4" max="4" width="14.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1528,221 +1529,218 @@
       <c r="BP1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" t="s">
+    </row>
+    <row r="2" spans="1:68" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>68</v>
       </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS2">
+        <v>100</v>
+      </c>
+      <c r="AT2">
+        <v>100</v>
+      </c>
+      <c r="AU2">
+        <v>100</v>
+      </c>
+      <c r="AV2">
+        <v>100</v>
+      </c>
+      <c r="AW2">
+        <v>100</v>
+      </c>
+      <c r="AX2">
+        <v>100</v>
+      </c>
+      <c r="AY2">
+        <v>100</v>
+      </c>
+      <c r="AZ2">
+        <v>100</v>
+      </c>
+      <c r="BA2">
+        <v>100</v>
+      </c>
+      <c r="BB2">
+        <v>100</v>
+      </c>
+      <c r="BC2">
+        <v>100</v>
+      </c>
+      <c r="BD2">
+        <v>100</v>
+      </c>
+      <c r="BE2">
+        <v>100</v>
+      </c>
+      <c r="BF2">
+        <v>100</v>
+      </c>
+      <c r="BG2">
+        <v>100</v>
+      </c>
+      <c r="BH2">
+        <v>100</v>
+      </c>
+      <c r="BI2">
+        <v>100</v>
+      </c>
+      <c r="BJ2">
+        <v>100</v>
+      </c>
+      <c r="BK2">
+        <v>100</v>
+      </c>
+      <c r="BL2">
+        <v>100</v>
+      </c>
+      <c r="BM2">
+        <v>100</v>
+      </c>
+      <c r="BN2">
+        <v>100</v>
+      </c>
+      <c r="BO2">
+        <v>100</v>
+      </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="3" spans="1:68" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
         <v>69</v>
       </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>72</v>
       </c>
-      <c r="AS2">
-        <v>100</v>
-      </c>
-      <c r="AT2">
-        <v>100</v>
-      </c>
-      <c r="AU2">
-        <v>100</v>
-      </c>
-      <c r="AV2">
-        <v>100</v>
-      </c>
-      <c r="AW2">
-        <v>100</v>
-      </c>
-      <c r="AX2">
-        <v>100</v>
-      </c>
-      <c r="AY2">
-        <v>100</v>
-      </c>
-      <c r="AZ2">
-        <v>100</v>
-      </c>
-      <c r="BA2">
-        <v>100</v>
-      </c>
-      <c r="BB2">
-        <v>100</v>
-      </c>
-      <c r="BC2">
-        <v>100</v>
-      </c>
-      <c r="BD2">
-        <v>100</v>
-      </c>
-      <c r="BE2">
-        <v>100</v>
-      </c>
-      <c r="BF2">
-        <v>100</v>
-      </c>
-      <c r="BG2">
-        <v>100</v>
-      </c>
-      <c r="BH2">
-        <v>100</v>
-      </c>
-      <c r="BI2">
-        <v>100</v>
-      </c>
-      <c r="BJ2">
-        <v>100</v>
-      </c>
-      <c r="BK2">
-        <v>100</v>
-      </c>
-      <c r="BL2">
-        <v>100</v>
-      </c>
-      <c r="BM2">
-        <v>100</v>
-      </c>
-      <c r="BN2">
-        <v>100</v>
-      </c>
-      <c r="BO2">
+      <c r="D3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI3">
+        <v>100</v>
+      </c>
+      <c r="AJ3">
+        <v>100</v>
+      </c>
+      <c r="AK3">
+        <v>100</v>
+      </c>
+      <c r="AL3">
+        <v>100</v>
+      </c>
+      <c r="AM3">
+        <v>100</v>
+      </c>
+      <c r="AN3">
+        <v>100</v>
+      </c>
+      <c r="AO3">
+        <v>100</v>
+      </c>
+      <c r="AP3">
+        <v>100</v>
+      </c>
+      <c r="AQ3">
+        <v>100</v>
+      </c>
+      <c r="AR3">
+        <v>100</v>
+      </c>
+      <c r="AS3">
+        <v>100</v>
+      </c>
+      <c r="AT3">
+        <v>100</v>
+      </c>
+      <c r="AU3">
+        <v>100</v>
+      </c>
+      <c r="AV3">
+        <v>100</v>
+      </c>
+      <c r="AW3">
+        <v>100</v>
+      </c>
+      <c r="AX3">
+        <v>100</v>
+      </c>
+      <c r="AY3">
+        <v>100</v>
+      </c>
+      <c r="AZ3">
+        <v>100</v>
+      </c>
+      <c r="BA3">
+        <v>100</v>
+      </c>
+      <c r="BB3">
+        <v>100</v>
+      </c>
+      <c r="BC3">
+        <v>100</v>
+      </c>
+      <c r="BD3">
+        <v>100</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>100</v>
+      </c>
+      <c r="BG3">
+        <v>100</v>
+      </c>
+      <c r="BH3">
+        <v>100</v>
+      </c>
+      <c r="BI3">
+        <v>100</v>
+      </c>
+      <c r="BJ3">
+        <v>100</v>
+      </c>
+      <c r="BK3">
+        <v>100</v>
+      </c>
+      <c r="BL3">
+        <v>100</v>
+      </c>
+      <c r="BM3">
+        <v>100</v>
+      </c>
+      <c r="BN3">
+        <v>100</v>
+      </c>
+      <c r="BO3">
+        <v>100</v>
+      </c>
+      <c r="BP3">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="4" spans="1:68" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
         <v>74</v>
       </c>
-      <c r="AI3">
-        <v>100</v>
-      </c>
-      <c r="AJ3">
-        <v>100</v>
-      </c>
-      <c r="AK3">
-        <v>100</v>
-      </c>
-      <c r="AL3">
-        <v>100</v>
-      </c>
-      <c r="AM3">
-        <v>100</v>
-      </c>
-      <c r="AN3">
-        <v>100</v>
-      </c>
-      <c r="AO3">
-        <v>100</v>
-      </c>
-      <c r="AP3">
-        <v>100</v>
-      </c>
-      <c r="AQ3">
-        <v>100</v>
-      </c>
-      <c r="AR3">
-        <v>100</v>
-      </c>
-      <c r="AS3">
-        <v>100</v>
-      </c>
-      <c r="AT3">
-        <v>100</v>
-      </c>
-      <c r="AU3">
-        <v>100</v>
-      </c>
-      <c r="AV3">
-        <v>100</v>
-      </c>
-      <c r="AW3">
-        <v>100</v>
-      </c>
-      <c r="AX3">
-        <v>100</v>
-      </c>
-      <c r="AY3">
-        <v>100</v>
-      </c>
-      <c r="AZ3">
-        <v>100</v>
-      </c>
-      <c r="BA3">
-        <v>100</v>
-      </c>
-      <c r="BB3">
-        <v>100</v>
-      </c>
-      <c r="BC3">
-        <v>100</v>
-      </c>
-      <c r="BD3">
-        <v>100</v>
-      </c>
-      <c r="BE3">
-        <v>100</v>
-      </c>
-      <c r="BF3">
-        <v>100</v>
-      </c>
-      <c r="BG3">
-        <v>100</v>
-      </c>
-      <c r="BH3">
-        <v>100</v>
-      </c>
-      <c r="BI3">
-        <v>100</v>
-      </c>
-      <c r="BJ3">
-        <v>100</v>
-      </c>
-      <c r="BK3">
-        <v>100</v>
-      </c>
-      <c r="BL3">
-        <v>100</v>
-      </c>
-      <c r="BM3">
-        <v>100</v>
-      </c>
-      <c r="BN3">
-        <v>100</v>
-      </c>
-      <c r="BO3">
-        <v>100</v>
-      </c>
-      <c r="BP3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>76</v>
       </c>
       <c r="E4">
         <v>16.8</v>
@@ -1937,18 +1935,18 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
       </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
       <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
       </c>
       <c r="AF5">
         <v>100</v>
@@ -1957,18 +1955,18 @@
         <v>99.3</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
         <v>79</v>
       </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
       <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" t="s">
         <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
       </c>
       <c r="AS6">
         <v>23.5</v>
@@ -2040,18 +2038,18 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
         <v>79</v>
       </c>
-      <c r="B7" t="s">
-        <v>80</v>
-      </c>
       <c r="C7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" t="s">
         <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
       </c>
       <c r="AQ7">
         <v>70.459999999999994</v>
@@ -2132,18 +2130,18 @@
         <v>95.6</v>
       </c>
     </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
         <v>79</v>
       </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
       <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
         <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
       </c>
       <c r="E8">
         <v>46.692999999999998</v>
@@ -2338,18 +2336,18 @@
         <v>27.806000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
         <v>79</v>
       </c>
-      <c r="B9" t="s">
-        <v>80</v>
-      </c>
       <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
         <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
       </c>
       <c r="AJ9">
         <v>17.2</v>
@@ -2403,18 +2401,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
         <v>81</v>
       </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
       <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
       </c>
       <c r="AS10">
         <v>38.5</v>
@@ -2486,18 +2484,18 @@
         <v>59.1</v>
       </c>
     </row>
-    <row r="11" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
         <v>81</v>
       </c>
-      <c r="B11" t="s">
-        <v>82</v>
-      </c>
       <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
         <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>74</v>
       </c>
       <c r="AL11">
         <v>65.400000000000006</v>
@@ -2593,18 +2591,18 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" t="s">
         <v>81</v>
       </c>
-      <c r="B12" t="s">
-        <v>82</v>
-      </c>
       <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
         <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>76</v>
       </c>
       <c r="E12">
         <v>47.158000000000001</v>
@@ -2799,18 +2797,18 @@
         <v>16.018999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:69" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:68" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
         <v>81</v>
       </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
       <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
         <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>78</v>
       </c>
       <c r="AL13">
         <v>52.8</v>
@@ -2861,183 +2859,183 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
         <v>84</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>85</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>86</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>87</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>89</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>90</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>91</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>92</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>93</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>94</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>95</v>
-      </c>
-      <c r="P1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
         <v>97</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>98</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>99</v>
       </c>
-      <c r="E2" t="s">
-        <v>100</v>
-      </c>
       <c r="F2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" t="s">
         <v>101</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" t="s">
         <v>103</v>
-      </c>
-      <c r="M2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
         <v>105</v>
       </c>
-      <c r="E3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="L3" t="s">
         <v>106</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>107</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
         <v>110</v>
       </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>111</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" t="s">
         <v>112</v>
       </c>
-      <c r="F4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
         <v>118</v>
       </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>119</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" t="s">
         <v>120</v>
       </c>
-      <c r="F5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H5" t="s">
-        <v>102</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="L5" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" t="s">
         <v>123</v>
-      </c>
-      <c r="N5" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
